--- a/data/excel/cammesa_diaria.xlsx
+++ b/data/excel/cammesa_diaria.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1749"/>
+  <dimension ref="A1:F1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35157,10 +35157,10 @@
         <v>16487.35080620174</v>
       </c>
       <c r="C1736" t="n">
-        <v>2514.053875</v>
+        <v>2515.043291666667</v>
       </c>
       <c r="D1736" t="n">
-        <v>13973.29693120173</v>
+        <v>13972.30751453507</v>
       </c>
       <c r="E1736" t="n">
         <v>12.10930013888889</v>
@@ -35177,10 +35177,10 @@
         <v>16484.77452957448</v>
       </c>
       <c r="C1737" t="n">
-        <v>2555.613916666666</v>
+        <v>2556.529083333333</v>
       </c>
       <c r="D1737" t="n">
-        <v>13929.16061290781</v>
+        <v>13928.24544624115</v>
       </c>
       <c r="E1737" t="n">
         <v>12.77228270833333</v>
@@ -35197,10 +35197,10 @@
         <v>15176.2188896618</v>
       </c>
       <c r="C1738" t="n">
-        <v>2424.628666666667</v>
+        <v>2424.641583333334</v>
       </c>
       <c r="D1738" t="n">
-        <v>12751.59022299514</v>
+        <v>12751.57730632847</v>
       </c>
       <c r="E1738" t="n">
         <v>14.56376454861111</v>
@@ -35217,10 +35217,10 @@
         <v>13881.71125946684</v>
       </c>
       <c r="C1739" t="n">
-        <v>2247.257958333334</v>
+        <v>2246.990208333334</v>
       </c>
       <c r="D1739" t="n">
-        <v>11634.45330113351</v>
+        <v>11634.72105113351</v>
       </c>
       <c r="E1739" t="n">
         <v>16.50436822916667</v>
@@ -35237,10 +35237,10 @@
         <v>15153.8427992342</v>
       </c>
       <c r="C1740" t="n">
-        <v>2443.271875</v>
+        <v>2443.9165</v>
       </c>
       <c r="D1740" t="n">
-        <v>12710.5709242342</v>
+        <v>12709.9262992342</v>
       </c>
       <c r="E1740" t="n">
         <v>17.79398517361111</v>
@@ -35257,10 +35257,10 @@
         <v>15691.64239642925</v>
       </c>
       <c r="C1741" t="n">
-        <v>2535.591833333333</v>
+        <v>2536.646958333333</v>
       </c>
       <c r="D1741" t="n">
-        <v>13156.05056309592</v>
+        <v>13154.99543809592</v>
       </c>
       <c r="E1741" t="n">
         <v>17.39960739583334</v>
@@ -35277,10 +35277,10 @@
         <v>16243.51336785955</v>
       </c>
       <c r="C1742" t="n">
-        <v>2493.250458333333</v>
+        <v>2494.31325</v>
       </c>
       <c r="D1742" t="n">
-        <v>13750.26290952622</v>
+        <v>13749.20011785955</v>
       </c>
       <c r="E1742" t="n">
         <v>17.42869708333333</v>
@@ -35297,10 +35297,10 @@
         <v>16286.37476947535</v>
       </c>
       <c r="C1743" t="n">
-        <v>2537.083166666667</v>
+        <v>2538.603333333333</v>
       </c>
       <c r="D1743" t="n">
-        <v>13749.29160280868</v>
+        <v>13747.77143614201</v>
       </c>
       <c r="E1743" t="n">
         <v>15.2770065625</v>
@@ -35317,10 +35317,10 @@
         <v>16740.69028495581</v>
       </c>
       <c r="C1744" t="n">
-        <v>2557.287666666667</v>
+        <v>2558.634791666667</v>
       </c>
       <c r="D1744" t="n">
-        <v>14183.40261828915</v>
+        <v>14182.05549328914</v>
       </c>
       <c r="E1744" t="n">
         <v>13.06309899305556</v>
@@ -35337,10 +35337,10 @@
         <v>15650.91810995278</v>
       </c>
       <c r="C1745" t="n">
-        <v>2405.705208333333</v>
+        <v>2406.114458333333</v>
       </c>
       <c r="D1745" t="n">
-        <v>13245.21290161944</v>
+        <v>13244.80365161944</v>
       </c>
       <c r="E1745" t="n">
         <v>12.959091875</v>
@@ -35357,10 +35357,10 @@
         <v>14656.79178874505</v>
       </c>
       <c r="C1746" t="n">
-        <v>2196.302416666666</v>
+        <v>2196.892041666667</v>
       </c>
       <c r="D1746" t="n">
-        <v>12460.48937207838</v>
+        <v>12459.89974707838</v>
       </c>
       <c r="E1746" t="n">
         <v>12.73901916666666</v>
@@ -35377,10 +35377,10 @@
         <v>15081.61301656536</v>
       </c>
       <c r="C1747" t="n">
-        <v>2137.888458333334</v>
+        <v>2160.98925</v>
       </c>
       <c r="D1747" t="n">
-        <v>12943.72455823203</v>
+        <v>12920.62376656536</v>
       </c>
       <c r="E1747" t="n">
         <v>13.09267246527778</v>
@@ -35397,10 +35397,10 @@
         <v>16109.40807310807</v>
       </c>
       <c r="C1748" t="n">
-        <v>2388.904583333333</v>
+        <v>2414.94675</v>
       </c>
       <c r="D1748" t="n">
-        <v>13720.50348977474</v>
+        <v>13694.46132310807</v>
       </c>
       <c r="E1748" t="n">
         <v>15.65734996527778</v>
@@ -35417,15 +35417,155 @@
         <v>15945.76033344722</v>
       </c>
       <c r="C1749" t="n">
-        <v>2437.666875</v>
+        <v>2467.164041666666</v>
       </c>
       <c r="D1749" t="n">
-        <v>13508.09345844722</v>
+        <v>13478.59629178055</v>
       </c>
       <c r="E1749" t="n">
         <v>15.91738590277778</v>
       </c>
       <c r="F1749" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>15895.38509934245</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>2482.570875</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>13412.81422434245</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>15.79603857638889</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>16390.47351930911</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>2514.01</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>13876.46351930912</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>13.06793222222223</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>15727.83408270304</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>2405.586125</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>13322.24795770304</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>10.95955913194444</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>14370.53148370139</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>2233.975833333333</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>12136.55565036805</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>12.49073430555556</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>15998.9464060678</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>2452.749041666667</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>13546.19736440113</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>13.61999083333334</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>15941.80310865086</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>2419.769416666667</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>13522.0336919842</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>15.80609565972222</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>15992.00917894705</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>2504.713833333333</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>13487.29534561372</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>16.74313649305555</v>
+      </c>
+      <c r="F1756" t="n">
         <v>1</v>
       </c>
     </row>
@@ -35499,7 +35639,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T19:45:47Z</t>
+          <t>2026-10-24T05:02:43Z</t>
         </is>
       </c>
     </row>
@@ -35511,7 +35651,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/data/excel/cammesa_diaria.xlsx
+++ b/data/excel/cammesa_diaria.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1756"/>
+  <dimension ref="A1:F1763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35154,13 +35154,13 @@
         <v>46296</v>
       </c>
       <c r="B1736" t="n">
-        <v>16487.35080620174</v>
+        <v>16541.50148386333</v>
       </c>
       <c r="C1736" t="n">
-        <v>2515.043291666667</v>
+        <v>2516.640625</v>
       </c>
       <c r="D1736" t="n">
-        <v>13972.30751453507</v>
+        <v>14024.86085886333</v>
       </c>
       <c r="E1736" t="n">
         <v>12.10930013888889</v>
@@ -35174,13 +35174,13 @@
         <v>46297</v>
       </c>
       <c r="B1737" t="n">
-        <v>16484.77452957448</v>
+        <v>16538.88484038153</v>
       </c>
       <c r="C1737" t="n">
-        <v>2556.529083333333</v>
+        <v>2557.895958333333</v>
       </c>
       <c r="D1737" t="n">
-        <v>13928.24544624115</v>
+        <v>13980.9888820482</v>
       </c>
       <c r="E1737" t="n">
         <v>12.77228270833333</v>
@@ -35194,13 +35194,13 @@
         <v>46298</v>
       </c>
       <c r="B1738" t="n">
-        <v>15176.2188896618</v>
+        <v>15225.84486807722</v>
       </c>
       <c r="C1738" t="n">
-        <v>2424.641583333334</v>
+        <v>2425.439208333333</v>
       </c>
       <c r="D1738" t="n">
-        <v>12751.57730632847</v>
+        <v>12800.40565974389</v>
       </c>
       <c r="E1738" t="n">
         <v>14.56376454861111</v>
@@ -35214,13 +35214,13 @@
         <v>46299</v>
       </c>
       <c r="B1739" t="n">
-        <v>13881.71125946684</v>
+        <v>13926.81943090097</v>
       </c>
       <c r="C1739" t="n">
-        <v>2246.990208333334</v>
+        <v>2247.78125</v>
       </c>
       <c r="D1739" t="n">
-        <v>11634.72105113351</v>
+        <v>11679.03818090097</v>
       </c>
       <c r="E1739" t="n">
         <v>16.50436822916667</v>
@@ -35234,13 +35234,13 @@
         <v>46300</v>
       </c>
       <c r="B1740" t="n">
-        <v>15153.8427992342</v>
+        <v>15203.23462748847</v>
       </c>
       <c r="C1740" t="n">
-        <v>2443.9165</v>
+        <v>2445.389041666667</v>
       </c>
       <c r="D1740" t="n">
-        <v>12709.9262992342</v>
+        <v>12757.84558582181</v>
       </c>
       <c r="E1740" t="n">
         <v>17.79398517361111</v>
@@ -35254,13 +35254,13 @@
         <v>46301</v>
       </c>
       <c r="B1741" t="n">
-        <v>15691.64239642925</v>
+        <v>15742.82560655521</v>
       </c>
       <c r="C1741" t="n">
-        <v>2536.646958333333</v>
+        <v>2538.141041666667</v>
       </c>
       <c r="D1741" t="n">
-        <v>13154.99543809592</v>
+        <v>13204.68456488854</v>
       </c>
       <c r="E1741" t="n">
         <v>17.39960739583334</v>
@@ -35274,13 +35274,13 @@
         <v>46302</v>
       </c>
       <c r="B1742" t="n">
-        <v>16243.51336785955</v>
+        <v>16296.69953548792</v>
       </c>
       <c r="C1742" t="n">
-        <v>2494.31325</v>
+        <v>2495.64275</v>
       </c>
       <c r="D1742" t="n">
-        <v>13749.20011785955</v>
+        <v>13801.05678548792</v>
       </c>
       <c r="E1742" t="n">
         <v>17.42869708333333</v>
@@ -35294,13 +35294,13 @@
         <v>46303</v>
       </c>
       <c r="B1743" t="n">
-        <v>16286.37476947535</v>
+        <v>16339.63296290056</v>
       </c>
       <c r="C1743" t="n">
-        <v>2538.603333333333</v>
+        <v>2539.605625</v>
       </c>
       <c r="D1743" t="n">
-        <v>13747.77143614201</v>
+        <v>13800.02733790056</v>
       </c>
       <c r="E1743" t="n">
         <v>15.2770065625</v>
@@ -35314,13 +35314,13 @@
         <v>46304</v>
       </c>
       <c r="B1744" t="n">
-        <v>16740.69028495581</v>
+        <v>16795.53171644951</v>
       </c>
       <c r="C1744" t="n">
         <v>2558.634791666667</v>
       </c>
       <c r="D1744" t="n">
-        <v>14182.05549328914</v>
+        <v>14236.89692478284</v>
       </c>
       <c r="E1744" t="n">
         <v>13.06309899305556</v>
@@ -35334,13 +35334,13 @@
         <v>46305</v>
       </c>
       <c r="B1745" t="n">
-        <v>15650.91810995278</v>
+        <v>15702.00676137972</v>
       </c>
       <c r="C1745" t="n">
         <v>2406.114458333333</v>
       </c>
       <c r="D1745" t="n">
-        <v>13244.80365161944</v>
+        <v>13295.89230304639</v>
       </c>
       <c r="E1745" t="n">
         <v>12.959091875</v>
@@ -35354,13 +35354,13 @@
         <v>46306</v>
       </c>
       <c r="B1746" t="n">
-        <v>14656.79178874505</v>
+        <v>14704.4258405784</v>
       </c>
       <c r="C1746" t="n">
         <v>2196.892041666667</v>
       </c>
       <c r="D1746" t="n">
-        <v>12459.89974707838</v>
+        <v>12507.53379891173</v>
       </c>
       <c r="E1746" t="n">
         <v>12.73901916666666</v>
@@ -35374,13 +35374,13 @@
         <v>46307</v>
       </c>
       <c r="B1747" t="n">
-        <v>15081.61301656536</v>
+        <v>15130.72624584715</v>
       </c>
       <c r="C1747" t="n">
-        <v>2160.98925</v>
+        <v>2161.129541666667</v>
       </c>
       <c r="D1747" t="n">
-        <v>12920.62376656536</v>
+        <v>12969.59670418049</v>
       </c>
       <c r="E1747" t="n">
         <v>13.09267246527778</v>
@@ -35394,13 +35394,13 @@
         <v>46308</v>
       </c>
       <c r="B1748" t="n">
-        <v>16109.40807310807</v>
+        <v>16162.05110738993</v>
       </c>
       <c r="C1748" t="n">
-        <v>2414.94675</v>
+        <v>2417.667375</v>
       </c>
       <c r="D1748" t="n">
-        <v>13694.46132310807</v>
+        <v>13744.38373238993</v>
       </c>
       <c r="E1748" t="n">
         <v>15.65734996527778</v>
@@ -35414,13 +35414,13 @@
         <v>46309</v>
       </c>
       <c r="B1749" t="n">
-        <v>15945.76033344722</v>
+        <v>15997.86877421778</v>
       </c>
       <c r="C1749" t="n">
-        <v>2467.164041666666</v>
+        <v>2472.819083333333</v>
       </c>
       <c r="D1749" t="n">
-        <v>13478.59629178055</v>
+        <v>13525.04969088444</v>
       </c>
       <c r="E1749" t="n">
         <v>15.91738590277778</v>
@@ -35434,13 +35434,13 @@
         <v>46310</v>
       </c>
       <c r="B1750" t="n">
-        <v>15895.38509934245</v>
+        <v>15947.36760883854</v>
       </c>
       <c r="C1750" t="n">
-        <v>2482.570875</v>
+        <v>2487.787083333334</v>
       </c>
       <c r="D1750" t="n">
-        <v>13412.81422434245</v>
+        <v>13459.58052550521</v>
       </c>
       <c r="E1750" t="n">
         <v>15.79603857638889</v>
@@ -35454,13 +35454,13 @@
         <v>46311</v>
       </c>
       <c r="B1751" t="n">
-        <v>16390.47351930911</v>
+        <v>16444.1705131891</v>
       </c>
       <c r="C1751" t="n">
-        <v>2514.01</v>
+        <v>2519.892416666667</v>
       </c>
       <c r="D1751" t="n">
-        <v>13876.46351930912</v>
+        <v>13924.27809652243</v>
       </c>
       <c r="E1751" t="n">
         <v>13.06793222222223</v>
@@ -35474,13 +35474,13 @@
         <v>46312</v>
       </c>
       <c r="B1752" t="n">
-        <v>15727.83408270304</v>
+        <v>15779.15992836229</v>
       </c>
       <c r="C1752" t="n">
-        <v>2405.586125</v>
+        <v>2408.620041666667</v>
       </c>
       <c r="D1752" t="n">
-        <v>13322.24795770304</v>
+        <v>13370.53988669563</v>
       </c>
       <c r="E1752" t="n">
         <v>10.95955913194444</v>
@@ -35494,13 +35494,13 @@
         <v>46313</v>
       </c>
       <c r="B1753" t="n">
-        <v>14370.53148370139</v>
+        <v>14417.16913700139</v>
       </c>
       <c r="C1753" t="n">
-        <v>2233.975833333333</v>
+        <v>2237.048125</v>
       </c>
       <c r="D1753" t="n">
-        <v>12136.55565036805</v>
+        <v>12180.12101200139</v>
       </c>
       <c r="E1753" t="n">
         <v>12.49073430555556</v>
@@ -35514,13 +35514,13 @@
         <v>46314</v>
       </c>
       <c r="B1754" t="n">
-        <v>15998.9464060678</v>
+        <v>16051.21937709743</v>
       </c>
       <c r="C1754" t="n">
-        <v>2452.749041666667</v>
+        <v>2459.576</v>
       </c>
       <c r="D1754" t="n">
-        <v>13546.19736440113</v>
+        <v>13591.64337709743</v>
       </c>
       <c r="E1754" t="n">
         <v>13.61999083333334</v>
@@ -35534,13 +35534,13 @@
         <v>46315</v>
       </c>
       <c r="B1755" t="n">
-        <v>15941.80310865086</v>
+        <v>15993.75388924125</v>
       </c>
       <c r="C1755" t="n">
-        <v>2419.769416666667</v>
+        <v>2479.516</v>
       </c>
       <c r="D1755" t="n">
-        <v>13522.0336919842</v>
+        <v>13514.23788924125</v>
       </c>
       <c r="E1755" t="n">
         <v>15.80609565972222</v>
@@ -35554,18 +35554,158 @@
         <v>46316</v>
       </c>
       <c r="B1756" t="n">
-        <v>15992.00917894705</v>
+        <v>16044.15275074375</v>
       </c>
       <c r="C1756" t="n">
-        <v>2504.713833333333</v>
+        <v>2506.815958333334</v>
       </c>
       <c r="D1756" t="n">
-        <v>13487.29534561372</v>
+        <v>13537.33679241042</v>
       </c>
       <c r="E1756" t="n">
         <v>16.74313649305555</v>
       </c>
       <c r="F1756" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>16106.51213664042</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>2479.8935</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>13626.61863664042</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>18.18093684027778</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1758" t="n">
+        <v>15847.4781160509</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>2484.384625</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>13363.0934910509</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>19.56412010416667</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B1759" t="n">
+        <v>14692.64622209722</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>2379.448791666666</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>12313.19743043055</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>14.75035003472222</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="2" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>13886.66168886437</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>2221.554916666667</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>11665.10677219771</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>13.43140361111111</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="2" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1761" t="n">
+        <v>15564.86833037528</v>
+      </c>
+      <c r="C1761" t="n">
+        <v>2428.057791666666</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>13136.81053870861</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>13.46121534722222</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="2" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1762" t="n">
+        <v>15664.14352281715</v>
+      </c>
+      <c r="C1762" t="n">
+        <v>2505.712</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>13158.43152281715</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>15.90720149305555</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="2" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1763" t="n">
+        <v>15647.68447318514</v>
+      </c>
+      <c r="C1763" t="n">
+        <v>2490.871708333333</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>13156.81276485181</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>17.25471840277777</v>
+      </c>
+      <c r="F1763" t="n">
         <v>1</v>
       </c>
     </row>
@@ -35639,7 +35779,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24T05:02:43Z</t>
+          <t>2026-10-31T06:18:29Z</t>
         </is>
       </c>
     </row>
@@ -35651,7 +35791,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
